--- a/artfynd/A 48033-2023 artfynd.xlsx
+++ b/artfynd/A 48033-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48033-2023 artfynd.xlsx
+++ b/artfynd/A 48033-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105249268</v>
+        <v>83255619</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,17 +710,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövsehult, trädid F55261, Sm</t>
+          <t>Pershult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515240.4469791054</v>
+        <v>515213</v>
       </c>
       <c r="R2" t="n">
-        <v>6390387.061804233</v>
+        <v>6390383</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +744,17 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>F55261</t>
+          <t>4176021A-C96D-4FDB-850F-86047A1FCA21</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-06-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-11-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-06-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-11-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +774,450 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Marielle Gustafsson, Malin Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>83255620</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Pershult, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>515241</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6390409</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hult</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>82A91E5E-CC08-417E-80B3-76F9E9F5DA23</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2007-11-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2007-11-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson, Malin Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>83255623</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Pershult, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>515222</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6390386</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hult</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>44C7B917-384D-4407-BC1D-11B596C82FBE</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2007-11-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2007-11-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson, Malin Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>105249267</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lövsehult, trädid F55262, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>515212</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6390374</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hult</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>F55262</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2013-06-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2013-06-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Stefan Gustafsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>105249268</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lövsehult, trädid F55261, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>515241</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6390387</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hult</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>F55261</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2013-06-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2013-06-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Stefan Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>

--- a/artfynd/A 48033-2023 artfynd.xlsx
+++ b/artfynd/A 48033-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83255619</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83255620</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83255623</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105249267</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,8 +1247,20 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105249268</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>